--- a/Excel_export/2025T144_heating030.xlsx
+++ b/Excel_export/2025T144_heating030.xlsx
@@ -893,16 +893,16 @@
     <t>UTC timestamp in ISO 8601 format</t>
   </si>
   <si>
-    <t>Raw GPS latitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
-  </si>
-  <si>
-    <t>Raw GPS longitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
-  </si>
-  <si>
-    <t>Quality-controlled latitude; interpolated to heating axes when needed</t>
-  </si>
-  <si>
-    <t>Quality-controlled longitude; interpolated to heating axes when needed</t>
+    <t>Raw GPS latitude on this data time axis</t>
+  </si>
+  <si>
+    <t>Raw GPS longitude on this data time axis</t>
+  </si>
+  <si>
+    <t>Quality-controlled latitude on this data time axis</t>
+  </si>
+  <si>
+    <t>Quality-controlled longitude on this data time axis</t>
   </si>
   <si>
     <t>1=original; 2=interpolated; 3=invalid; 4=edge extrapolated; 5=long-gap filled</t>
@@ -2077,10 +2077,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>84.7881</v>
+        <v>84.787999999999997</v>
       </c>
       <c r="C2" s="0">
-        <v>13.942399999999999</v>
+        <v>13.9406</v>
       </c>
       <c r="D2" s="0">
         <v>84.787999999999997</v>
@@ -2834,10 +2834,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>84.7102</v>
+        <v>84.675600000000003</v>
       </c>
       <c r="C3" s="0">
-        <v>14.129200000000001</v>
+        <v>14.036199999999999</v>
       </c>
       <c r="D3" s="0">
         <v>84.7102</v>
@@ -3591,10 +3591,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>84.6066</v>
+        <v>84.614800000000002</v>
       </c>
       <c r="C4" s="0">
-        <v>13.852</v>
+        <v>13.4809</v>
       </c>
       <c r="D4" s="0">
         <v>84.640699999999995</v>
@@ -5105,10 +5105,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>84.576499999999996</v>
+        <v>84.542000000000002</v>
       </c>
       <c r="C6" s="0">
-        <v>13.3918</v>
+        <v>13.305199999999999</v>
       </c>
       <c r="D6" s="0">
         <v>84.568299999999994</v>
@@ -5862,10 +5862,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>84.507199999999997</v>
+        <v>84.507300000000001</v>
       </c>
       <c r="C7" s="0">
-        <v>13.2212</v>
+        <v>13.219099999999999</v>
       </c>
       <c r="D7" s="0">
         <v>84.507199999999997</v>
@@ -6619,10 +6619,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>84.369399999999999</v>
+        <v>84.378100000000003</v>
       </c>
       <c r="C8" s="0">
-        <v>14.389200000000001</v>
+        <v>14.036199999999999</v>
       </c>
       <c r="D8" s="0">
         <v>84.378100000000003</v>
@@ -7376,10 +7376,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>84.247600000000006</v>
+        <v>83.430700000000002</v>
       </c>
       <c r="C9" s="0">
-        <v>14.814399999999999</v>
+        <v>30.211300000000001</v>
       </c>
       <c r="D9" s="0">
         <v>84.247600000000006</v>
@@ -8133,10 +8133,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>83.4285</v>
+        <v>84.123699999999999</v>
       </c>
       <c r="C10" s="0">
-        <v>28.305099999999999</v>
+        <v>13.781599999999999</v>
       </c>
       <c r="D10" s="0">
         <v>84.119399999999999</v>
@@ -8890,10 +8890,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>84.019999999999996</v>
+        <v>84.011399999999995</v>
       </c>
       <c r="C11" s="0">
-        <v>13.535</v>
+        <v>13.8697</v>
       </c>
       <c r="D11" s="0">
         <v>84.054400000000001</v>
@@ -9647,10 +9647,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>83.966300000000004</v>
+        <v>83.931799999999996</v>
       </c>
       <c r="C12" s="0">
-        <v>12.713100000000001</v>
+        <v>12.639099999999999</v>
       </c>
       <c r="D12" s="0">
         <v>83.966399999999993</v>
@@ -10404,10 +10404,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>83.342200000000005</v>
+        <v>83.872900000000001</v>
       </c>
       <c r="C13" s="0">
-        <v>23.473600000000001</v>
+        <v>13.5479</v>
       </c>
       <c r="D13" s="0">
         <v>83.902900000000002</v>
@@ -11161,10 +11161,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>83.790599999999998</v>
+        <v>83.9666</v>
       </c>
       <c r="C14" s="0">
-        <v>15.081099999999999</v>
+        <v>12.7136</v>
       </c>
       <c r="D14" s="0">
         <v>83.8249</v>
@@ -11918,10 +11918,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>83.472999999999999</v>
+        <v>83.392399999999995</v>
       </c>
       <c r="C15" s="0">
-        <v>21.6038</v>
+        <v>21.6858</v>
       </c>
       <c r="D15" s="0">
         <v>83.805899999999994</v>
@@ -12675,10 +12675,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>83.621700000000004</v>
+        <v>83.456100000000006</v>
       </c>
       <c r="C16" s="0">
-        <v>18.019300000000001</v>
+        <v>20.224900000000002</v>
       </c>
       <c r="D16" s="0">
         <v>83.773799999999994</v>
@@ -13432,10 +13432,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>83.511099999999999</v>
+        <v>83.654600000000002</v>
       </c>
       <c r="C17" s="0">
-        <v>20.732099999999999</v>
+        <v>18.127500000000001</v>
       </c>
       <c r="D17" s="0">
         <v>83.727199999999996</v>
@@ -14189,10 +14189,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>83.7333</v>
+        <v>83.687799999999996</v>
       </c>
       <c r="C18" s="0">
-        <v>19.056799999999999</v>
+        <v>19.2593</v>
       </c>
       <c r="D18" s="0">
         <v>83.744799999999998</v>
@@ -14946,10 +14946,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>83.845799999999997</v>
+        <v>83.846000000000004</v>
       </c>
       <c r="C19" s="0">
-        <v>18.023099999999999</v>
+        <v>18.0121</v>
       </c>
       <c r="D19" s="0">
         <v>83.766800000000003</v>
@@ -15703,10 +15703,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>83.756</v>
+        <v>83.797799999999995</v>
       </c>
       <c r="C20" s="0">
-        <v>20.5549</v>
+        <v>20.3231</v>
       </c>
       <c r="D20" s="0">
         <v>83.752099999999999</v>
@@ -16460,10 +16460,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>83.971800000000002</v>
+        <v>84.108999999999995</v>
       </c>
       <c r="C21" s="0">
-        <v>19.841699999999999</v>
+        <v>18.1038</v>
       </c>
       <c r="D21" s="0">
         <v>83.859099999999998</v>
@@ -17217,10 +17217,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>84.347800000000007</v>
+        <v>84.393799999999999</v>
       </c>
       <c r="C22" s="0">
-        <v>17.759899999999998</v>
+        <v>17.507200000000001</v>
       </c>
       <c r="D22" s="0">
         <v>84.027900000000002</v>
@@ -17974,10 +17974,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>84.441299999999998</v>
+        <v>84.107799999999997</v>
       </c>
       <c r="C23" s="0">
-        <v>18.492000000000001</v>
+        <v>22.190300000000001</v>
       </c>
       <c r="D23" s="0">
         <v>84.143000000000001</v>
@@ -18731,10 +18731,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>84.290300000000002</v>
+        <v>84.551299999999998</v>
       </c>
       <c r="C24" s="0">
-        <v>20.617799999999999</v>
+        <v>17.241499999999998</v>
       </c>
       <c r="D24" s="0">
         <v>84.263599999999997</v>
@@ -19488,10 +19488,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>84.652799999999999</v>
+        <v>84.742199999999997</v>
       </c>
       <c r="C25" s="0">
-        <v>16.391400000000001</v>
+        <v>15.837999999999999</v>
       </c>
       <c r="D25" s="0">
         <v>84.296800000000005</v>
@@ -20245,10 +20245,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>84.711500000000001</v>
+        <v>84.864500000000007</v>
       </c>
       <c r="C26" s="0">
-        <v>16.985299999999999</v>
+        <v>15.3956</v>
       </c>
       <c r="D26" s="0">
         <v>84.316299999999998</v>
@@ -21002,10 +21002,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>84.501599999999996</v>
+        <v>84.455600000000004</v>
       </c>
       <c r="C27" s="0">
-        <v>21.044499999999999</v>
+        <v>21.250499999999999</v>
       </c>
       <c r="D27" s="0">
         <v>84.4255</v>
@@ -21759,10 +21759,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>85.034499999999994</v>
+        <v>85.083500000000001</v>
       </c>
       <c r="C28" s="0">
-        <v>15.972300000000001</v>
+        <v>15.6584</v>
       </c>
       <c r="D28" s="0">
         <v>84.481499999999997</v>
@@ -22516,10 +22516,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>85.061700000000002</v>
+        <v>85.205699999999993</v>
       </c>
       <c r="C29" s="0">
-        <v>16.4754</v>
+        <v>15.1799</v>
       </c>
       <c r="D29" s="0">
         <v>84.495400000000004</v>
@@ -23273,10 +23273,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>84.733000000000004</v>
+        <v>84.555199999999999</v>
       </c>
       <c r="C30" s="0">
-        <v>19.912600000000001</v>
+        <v>21.661200000000001</v>
       </c>
       <c r="D30" s="0">
         <v>84.638000000000005</v>
@@ -24030,10 +24030,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>85.305999999999997</v>
+        <v>84.650999999999996</v>
       </c>
       <c r="C31" s="0">
-        <v>15.5382</v>
+        <v>21.230599999999999</v>
       </c>
       <c r="D31" s="0">
         <v>84.638000000000005</v>
@@ -24787,10 +24787,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>84.742199999999997</v>
+        <v>85.440399999999997</v>
       </c>
       <c r="C32" s="0">
-        <v>20.770199999999999</v>
+        <v>14.5829</v>
       </c>
       <c r="D32" s="0">
         <v>84.743200000000002</v>
@@ -25544,10 +25544,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>84.811800000000005</v>
+        <v>84.722300000000004</v>
       </c>
       <c r="C33" s="0">
-        <v>19.795999999999999</v>
+        <v>20.282599999999999</v>
       </c>
       <c r="D33" s="0">
         <v>84.743200000000002</v>
@@ -26307,7 +26307,7 @@
   <cols>
     <col min="1" max="1" width="73.5703125" customWidth="true"/>
     <col min="2" max="2" width="6" customWidth="true"/>
-    <col min="3" max="3" width="83.85546875" customWidth="true"/>
+    <col min="3" max="3" width="75.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
